--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="64959230"/>
-        <c:axId val="5713901"/>
+        <c:axId val="67926815"/>
+        <c:axId val="10022376"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="64959230"/>
+        <c:axId val="67926815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5713901"/>
+        <c:crossAx val="10022376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="5713901"/>
+        <c:axId val="10022376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64959230"/>
+        <c:crossAx val="67926815"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>645480</xdr:colOff>
+      <xdr:colOff>645120</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>204120</xdr:rowOff>
+      <xdr:rowOff>203760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4552200" cy="2737080"/>
+        <a:ext cx="4551840" cy="2736720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R137"/>
+  <dimension ref="A1:R138"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>787.5</v>
+        <v>789.197080291971</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44806.5</v>
+        <v>44808.197080292</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1297.00676173349</v>
+        <v>1298.58594181149</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45316.0067617335</v>
+        <v>45317.5859418115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>903.308823529412</v>
+        <v>905.255474452555</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44922.3088235294</v>
+        <v>44924.2554744526</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1421.91913043977</v>
+        <v>1423.65039848675</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45440.9191304398</v>
+        <v>45442.6503984868</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1366.54411764706</v>
+        <v>1369.48905109489</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45385.5441176471</v>
+        <v>45388.4890510949</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>1713.38132408774</v>
+        <v>1715.46746406237</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>45732.3813240877</v>
+        <v>45734.4674640624</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2038.23529411765</v>
+        <v>2042.62773722628</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46057.2352941177</v>
+        <v>46061.6277372263</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2065.21782927708</v>
+        <v>2067.73235036436</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46084.2178292771</v>
+        <v>46086.7323503644</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3068.93382352941</v>
+        <v>3075.54744525547</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47087.9338235294</v>
+        <v>47094.5474452555</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>2727.25338342034</v>
+        <v>2730.57397074326</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>46746.2533834203</v>
+        <v>46749.5739707433</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3404.77941176471</v>
+        <v>3412.11678832117</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47423.7794117647</v>
+        <v>47431.1167883212</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>2835.51076963245</v>
+        <v>2838.96316652849</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>46854.5107696325</v>
+        <v>46857.9631665285</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3404.77941176471</v>
+        <v>3412.11678832117</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47423.7794117647</v>
+        <v>47431.1167883212</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>2835.51076963245</v>
+        <v>2838.96316652849</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>46854.5107696325</v>
+        <v>46857.9631665285</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.5808823529412</v>
+        <v>11.6058394160584</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.08187281177125</v>
+        <v>2.0844076112544</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7717,7 +7717,7 @@
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
-        <v>916</v>
+        <v>1001</v>
       </c>
       <c r="B136" s="1" t="str">
         <f aca="false">"卷"&amp;ROW(B135)</f>
@@ -7751,7 +7751,7 @@
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
-        <v>917</v>
+        <v>1002</v>
       </c>
       <c r="B137" s="1" t="str">
         <f aca="false">"卷"&amp;ROW(B136)</f>
@@ -7781,6 +7781,41 @@
       <c r="I137" s="1" t="n">
         <f aca="false">E137/H137</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B138" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B137)</f>
+        <v>卷137</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <f aca="false">D137+1</f>
+        <v>46060</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <f aca="false">D138-C138+1</f>
+        <v>15</v>
+      </c>
+      <c r="F138" s="1" t="n">
+        <f aca="false">G137+1</f>
+        <v>490</v>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>492</v>
+      </c>
+      <c r="H138" s="1" t="n">
+        <f aca="false">IF(F138*G138&lt;0,ABS(F138)+ABS(G138),G138-F138+1)</f>
+        <v>3</v>
+      </c>
+      <c r="I138" s="1" t="n">
+        <f aca="false">E138/H138</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11660,96 +11695,96 @@
       <c r="A135" s="1" t="n">
         <v>916</v>
       </c>
-      <c r="B135" s="1" t="str">
+      <c r="B135" s="1" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,2,)</f>
-        <v>卷135</v>
+        <v>#N/A</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D135" s="1" t="n">
+      <c r="D135" s="1" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,6,)</f>
-        <v>479</v>
-      </c>
-      <c r="E135" s="1" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="E135" s="1" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,7,)</f>
-        <v>483</v>
-      </c>
-      <c r="I135" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I135" s="1" t="e">
         <f aca="false">A135&amp;"|"&amp;"["&amp;B135&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B135,"卷","")&amp;".html)|"&amp;C135&amp;"|"&amp;D135&amp;"|"&amp;E135&amp;"|"&amp;H135</f>
-        <v>916|[卷135](9_筆記/资治通鉴135.html)|宋紀十六|479|483|</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="B136" s="1" t="e">
+      <c r="B136" s="1" t="str">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷135</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D136" s="1" t="e">
+      <c r="D136" s="1" t="n">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E136" s="1" t="e">
+        <v>479</v>
+      </c>
+      <c r="E136" s="1" t="n">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I136" s="1" t="e">
+        <v>483</v>
+      </c>
+      <c r="I136" s="1" t="str">
         <f aca="false">A136&amp;"|"&amp;"["&amp;B136&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B136,"卷","")&amp;".html)|"&amp;C136&amp;"|"&amp;D136&amp;"|"&amp;E136&amp;"|"&amp;H136</f>
-        <v>#N/A</v>
+        <v>1001|[卷135](9_筆記/资治通鉴135.html)|齊紀一|479|483|</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="B137" s="1" t="e">
+      <c r="B137" s="1" t="str">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷136</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D137" s="1" t="e">
+      <c r="D137" s="1" t="n">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E137" s="1" t="e">
+        <v>484</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I137" s="1" t="e">
+        <v>489</v>
+      </c>
+      <c r="I137" s="1" t="str">
         <f aca="false">A137&amp;"|"&amp;"["&amp;B137&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B137,"卷","")&amp;".html)|"&amp;C137&amp;"|"&amp;D137&amp;"|"&amp;E137&amp;"|"&amp;H137</f>
-        <v>#N/A</v>
+        <v>1002|[卷136](9_筆記/资治通鉴136.html)|齊紀二|484|489|</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="B138" s="1" t="e">
+      <c r="B138" s="1" t="str">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷137</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D138" s="1" t="e">
+      <c r="D138" s="1" t="n">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E138" s="1" t="e">
+        <v>490</v>
+      </c>
+      <c r="E138" s="1" t="n">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I138" s="1" t="e">
+        <v>492</v>
+      </c>
+      <c r="I138" s="1" t="str">
         <f aca="false">A138&amp;"|"&amp;"["&amp;B138&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B138,"卷","")&amp;".html)|"&amp;C138&amp;"|"&amp;D138&amp;"|"&amp;E138&amp;"|"&amp;H138</f>
-        <v>#N/A</v>
+        <v>1003|[卷137](9_筆記/资治通鉴137.html)|齊紀三|490|492|</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="67926815"/>
-        <c:axId val="10022376"/>
+        <c:axId val="1678165"/>
+        <c:axId val="70170856"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="67926815"/>
+        <c:axId val="1678165"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10022376"/>
+        <c:crossAx val="70170856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="10022376"/>
+        <c:axId val="70170856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67926815"/>
+        <c:crossAx val="1678165"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>645120</xdr:colOff>
+      <xdr:colOff>644760</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>203760</xdr:rowOff>
+      <xdr:rowOff>203400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4551840" cy="2736720"/>
+        <a:ext cx="4551480" cy="2736360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:R139"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>789.197080291971</v>
+        <v>786.927536231884</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44808.197080292</v>
+        <v>44805.9275362319</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1298.58594181149</v>
+        <v>1311.36767584</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45317.5859418115</v>
+        <v>45330.36767584</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>905.255474452555</v>
+        <v>902.652173913043</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44924.2554744526</v>
+        <v>44921.652173913</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1423.65039848675</v>
+        <v>1437.66311813599</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45442.6503984868</v>
+        <v>45456.663118136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1369.48905109489</v>
+        <v>1365.55072463768</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45388.4890510949</v>
+        <v>45384.5507246377</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>1715.46746406237</v>
+        <v>1732.3524834933</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>45734.4674640624</v>
+        <v>45751.3524834933</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2042.62773722628</v>
+        <v>2036.75362318841</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46061.6277372263</v>
+        <v>46055.7536231884</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2067.73235036436</v>
+        <v>2088.08464596033</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46086.7323503644</v>
+        <v>46107.0846459603</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3075.54744525547</v>
+        <v>3066.70289855072</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47094.5474452555</v>
+        <v>47085.7028985507</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>2730.57397074326</v>
+        <v>2757.45049012906</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>46749.5739707433</v>
+        <v>46776.4504901291</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3412.11678832117</v>
+        <v>3402.30434782609</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47431.1167883212</v>
+        <v>47421.3043478261</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>2838.96316652849</v>
+        <v>2866.90654011892</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>46857.9631665285</v>
+        <v>46885.9065401189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3412.11678832117</v>
+        <v>3402.30434782609</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47431.1167883212</v>
+        <v>47421.3043478261</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>2838.96316652849</v>
+        <v>2866.90654011892</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>46857.9631665285</v>
+        <v>46885.9065401189</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.6058394160584</v>
+        <v>11.5724637681159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.0844076112544</v>
+        <v>2.10492403826646</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7816,6 +7816,40 @@
       <c r="I138" s="1" t="n">
         <f aca="false">E138/H138</f>
         <v>5</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B139" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B138)</f>
+        <v>卷138</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <f aca="false">D139-C139+1</f>
+        <v>7</v>
+      </c>
+      <c r="F139" s="1" t="n">
+        <f aca="false">G138+1</f>
+        <v>493</v>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>493</v>
+      </c>
+      <c r="H139" s="1" t="n">
+        <f aca="false">IF(F139*G139&lt;0,ABS(F139)+ABS(G139),G139-F139+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I139" s="1" t="n">
+        <f aca="false">E139/H139</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -11691,7 +11725,7 @@
         <v>915|[卷133](9_筆記/资治通鉴133.html)|宋紀十五|471|475|</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
         <v>916</v>
       </c>
@@ -11715,7 +11749,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
         <v>1001</v>
       </c>
@@ -11739,7 +11773,7 @@
         <v>1001|[卷135](9_筆記/资治通鉴135.html)|齊紀一|479|483|</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
         <v>1002</v>
       </c>
@@ -11763,7 +11797,7 @@
         <v>1002|[卷136](9_筆記/资治通鉴136.html)|齊紀二|484|489|</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
         <v>1003</v>
       </c>
@@ -11791,24 +11825,24 @@
       <c r="A139" s="1" t="n">
         <v>1004</v>
       </c>
-      <c r="B139" s="1" t="e">
+      <c r="B139" s="1" t="str">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷138</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D139" s="1" t="e">
+      <c r="D139" s="1" t="n">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E139" s="1" t="e">
+        <v>493</v>
+      </c>
+      <c r="E139" s="1" t="n">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I139" s="1" t="e">
+        <v>493</v>
+      </c>
+      <c r="I139" s="1" t="str">
         <f aca="false">A139&amp;"|"&amp;"["&amp;B139&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B139,"卷","")&amp;".html)|"&amp;C139&amp;"|"&amp;D139&amp;"|"&amp;E139&amp;"|"&amp;H139</f>
-        <v>#N/A</v>
+        <v>1004|[卷138](9_筆記/资治通鉴138.html)|齊紀四|493|493|</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1678165"/>
-        <c:axId val="70170856"/>
+        <c:axId val="63783803"/>
+        <c:axId val="43885950"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1678165"/>
+        <c:axId val="63783803"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70170856"/>
+        <c:crossAx val="43885950"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="70170856"/>
+        <c:axId val="43885950"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1678165"/>
+        <c:crossAx val="63783803"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>644760</xdr:colOff>
+      <xdr:colOff>644400</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>203400</xdr:rowOff>
+      <xdr:rowOff>203040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4551480" cy="2736360"/>
+        <a:ext cx="4551120" cy="2736000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R139"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>786.927536231884</v>
+        <v>789.58273381295</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44805.9275362319</v>
+        <v>44808.582733813</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1311.36767584</v>
+        <v>1379.75428267348</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45330.36767584</v>
+        <v>45398.7542826735</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>902.652173913043</v>
+        <v>905.697841726619</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44921.652173913</v>
+        <v>44924.6978417266</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1437.66311813599</v>
+        <v>1512.63591503368</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45456.663118136</v>
+        <v>45531.6359150337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1365.55072463768</v>
+        <v>1370.1582733813</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45384.5507246377</v>
+        <v>45389.1582733813</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>1732.3524834933</v>
+        <v>1822.6930572075</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>45751.3524834933</v>
+        <v>45841.6930572075</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2036.75362318841</v>
+        <v>2043.62589928058</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46055.7536231884</v>
+        <v>46062.6258992806</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2088.08464596033</v>
+        <v>2196.97632168875</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46107.0846459603</v>
+        <v>46215.9763216887</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3066.70289855072</v>
+        <v>3077.05035971223</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47085.7028985507</v>
+        <v>47096.0503597122</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>2757.45049012906</v>
+        <v>2901.24897319784</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>46776.4504901291</v>
+        <v>46920.2489731978</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3402.30434782609</v>
+        <v>3413.78417266187</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47421.3043478261</v>
+        <v>47432.7841726619</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>2866.90654011892</v>
+        <v>3016.41305457668</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>46885.9065401189</v>
+        <v>47035.4130545767</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3402.30434782609</v>
+        <v>3413.78417266187</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47421.3043478261</v>
+        <v>47432.7841726619</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>2866.90654011892</v>
+        <v>3016.41305457668</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>46885.9065401189</v>
+        <v>47035.4130545767</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.5724637681159</v>
+        <v>11.6115107913669</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.10492403826646</v>
+        <v>2.21469387267011</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7850,6 +7850,41 @@
       <c r="I139" s="1" t="n">
         <f aca="false">E139/H139</f>
         <v>7</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B140" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B139)</f>
+        <v>卷139</v>
+      </c>
+      <c r="C140" s="2" t="n">
+        <f aca="false">D139+1</f>
+        <v>46083</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E140" s="1" t="n">
+        <f aca="false">D140-C140+1</f>
+        <v>17</v>
+      </c>
+      <c r="F140" s="1" t="n">
+        <f aca="false">G139+1</f>
+        <v>494</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>494</v>
+      </c>
+      <c r="H140" s="1" t="n">
+        <f aca="false">IF(F140*G140&lt;0,ABS(F140)+ABS(G140),G140-F140+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I140" s="1" t="n">
+        <f aca="false">E140/H140</f>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -11821,7 +11856,7 @@
         <v>1003|[卷137](9_筆記/资治通鉴137.html)|齊紀三|490|492|</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
         <v>1004</v>
       </c>
@@ -11849,24 +11884,24 @@
       <c r="A140" s="1" t="n">
         <v>1005</v>
       </c>
-      <c r="B140" s="1" t="e">
+      <c r="B140" s="1" t="str">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷139</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D140" s="1" t="e">
+      <c r="D140" s="1" t="n">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E140" s="1" t="e">
+        <v>494</v>
+      </c>
+      <c r="E140" s="1" t="n">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I140" s="1" t="e">
+        <v>494</v>
+      </c>
+      <c r="I140" s="1" t="str">
         <f aca="false">A140&amp;"|"&amp;"["&amp;B140&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B140,"卷","")&amp;".html)|"&amp;C140&amp;"|"&amp;D140&amp;"|"&amp;E140&amp;"|"&amp;H140</f>
-        <v>#N/A</v>
+        <v>1005|[卷139](9_筆記/资治通鉴139.html)|齊紀五|494|494|</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="63783803"/>
-        <c:axId val="43885950"/>
+        <c:axId val="17214200"/>
+        <c:axId val="51105084"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="63783803"/>
+        <c:axId val="17214200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43885950"/>
+        <c:crossAx val="51105084"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="43885950"/>
+        <c:axId val="51105084"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63783803"/>
+        <c:crossAx val="17214200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>644400</xdr:colOff>
+      <xdr:colOff>644040</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>203040</xdr:rowOff>
+      <xdr:rowOff>202680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4551120" cy="2736000"/>
+        <a:ext cx="4550760" cy="2735640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>789.58273381295</v>
+        <v>792.2</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44808.582733813</v>
+        <v>44811.2</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1379.75428267348</v>
+        <v>1399.04908022303</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45398.7542826735</v>
+        <v>45418.049080223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>905.697841726619</v>
+        <v>908.7</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44924.6978417266</v>
+        <v>44927.7</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1512.63591503368</v>
+        <v>1533.78895953825</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45531.6359150337</v>
+        <v>45552.7889595383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1370.1582733813</v>
+        <v>1374.7</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45389.1582733813</v>
+        <v>45393.7</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>1822.6930572075</v>
+        <v>1848.18201127377</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>45841.6930572075</v>
+        <v>45867.1820112738</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2043.62589928058</v>
+        <v>2050.4</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46062.6258992806</v>
+        <v>46069.4</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2196.97632168875</v>
+        <v>2227.69933801163</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46215.9763216887</v>
+        <v>46246.6993380116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3077.05035971223</v>
+        <v>3087.25</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47096.0503597122</v>
+        <v>47106.25</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>2901.24897319784</v>
+        <v>2941.8206983823</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>46920.2489731978</v>
+        <v>46960.8206983823</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3413.78417266187</v>
+        <v>3425.1</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47432.7841726619</v>
+        <v>47444.1</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>3016.41305457668</v>
+        <v>3058.59526045549</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>47035.4130545767</v>
+        <v>47077.5952604555</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3413.78417266187</v>
+        <v>3425.1</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47432.7841726619</v>
+        <v>47444.1</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>3016.41305457668</v>
+        <v>3058.59526045549</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>47035.4130545767</v>
+        <v>47077.5952604555</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.6115107913669</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.21469387267011</v>
+        <v>2.24566465525366</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7885,6 +7885,40 @@
       <c r="I140" s="1" t="n">
         <f aca="false">E140/H140</f>
         <v>17</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B141" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B140)</f>
+        <v>卷140</v>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="E141" s="1" t="n">
+        <f aca="false">D141-C141+1</f>
+        <v>17</v>
+      </c>
+      <c r="F141" s="1" t="n">
+        <f aca="false">G140+1</f>
+        <v>495</v>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>496</v>
+      </c>
+      <c r="H141" s="1" t="n">
+        <f aca="false">IF(F141*G141&lt;0,ABS(F141)+ABS(G141),G141-F141+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I141" s="1" t="n">
+        <f aca="false">E141/H141</f>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -11880,7 +11914,7 @@
         <v>1004|[卷138](9_筆記/资治通鉴138.html)|齊紀四|493|493|</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="n">
         <v>1005</v>
       </c>
@@ -11908,24 +11942,24 @@
       <c r="A141" s="1" t="n">
         <v>1006</v>
       </c>
-      <c r="B141" s="1" t="e">
+      <c r="B141" s="1" t="str">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷140</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D141" s="1" t="e">
+      <c r="D141" s="1" t="n">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E141" s="1" t="e">
+        <v>495</v>
+      </c>
+      <c r="E141" s="1" t="n">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I141" s="1" t="e">
+        <v>496</v>
+      </c>
+      <c r="I141" s="1" t="str">
         <f aca="false">A141&amp;"|"&amp;"["&amp;B141&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B141,"卷","")&amp;".html)|"&amp;C141&amp;"|"&amp;D141&amp;"|"&amp;E141&amp;"|"&amp;H141</f>
-        <v>#N/A</v>
+        <v>1006|[卷140](9_筆記/资治通鉴140.html)|齊紀六|495|496|</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="17214200"/>
-        <c:axId val="51105084"/>
+        <c:axId val="76972386"/>
+        <c:axId val="47824912"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="17214200"/>
+        <c:axId val="76972386"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51105084"/>
+        <c:crossAx val="47824912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="51105084"/>
+        <c:axId val="47824912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17214200"/>
+        <c:crossAx val="76972386"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>644040</xdr:colOff>
+      <xdr:colOff>643680</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>202680</xdr:rowOff>
+      <xdr:rowOff>202320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4550760" cy="2735640"/>
+        <a:ext cx="4550400" cy="2735280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R141"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>792.2</v>
+        <v>798.156028368794</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44811.2</v>
+        <v>44817.1560283688</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1399.04908022303</v>
+        <v>1436.74354656248</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45418.049080223</v>
+        <v>45455.7435465625</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>908.7</v>
+        <v>915.531914893617</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44927.7</v>
+        <v>44934.5319148936</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1533.78895953825</v>
+        <v>1575.11371156047</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45552.7889595383</v>
+        <v>45594.1137115605</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1374.7</v>
+        <v>1385.03546099291</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45393.7</v>
+        <v>45404.0354609929</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>1848.18201127377</v>
+        <v>1897.97742988912</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>45867.1820112738</v>
+        <v>45916.9774298891</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2050.4</v>
+        <v>2065.81560283688</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46069.4</v>
+        <v>46084.8156028369</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2227.69933801163</v>
+        <v>2287.72006130013</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46246.6993380116</v>
+        <v>46306.7200613001</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3087.25</v>
+        <v>3110.4609929078</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47106.25</v>
+        <v>47129.4609929078</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>2941.8206983823</v>
+        <v>3021.08193578948</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>46960.8206983823</v>
+        <v>47040.0819357895</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3425.1</v>
+        <v>3450.85106382979</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47444.1</v>
+        <v>47469.8510638298</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>3058.59526045549</v>
+        <v>3141.00274545441</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>47077.5952604555</v>
+        <v>47160.0027454544</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3425.1</v>
+        <v>3450.85106382979</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47444.1</v>
+        <v>47469.8510638298</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>3058.59526045549</v>
+        <v>3141.00274545441</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>47077.5952604555</v>
+        <v>47160.0027454544</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.65</v>
+        <v>11.7375886524823</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.24566465525366</v>
+        <v>2.30616941663319</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7919,6 +7919,40 @@
       <c r="I141" s="1" t="n">
         <f aca="false">E141/H141</f>
         <v>8.5</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B142" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B141)</f>
+        <v>卷141</v>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E142" s="1" t="n">
+        <f aca="false">D142-C142+1</f>
+        <v>24</v>
+      </c>
+      <c r="F142" s="1" t="n">
+        <f aca="false">G141+1</f>
+        <v>497</v>
+      </c>
+      <c r="G142" s="1" t="n">
+        <v>498</v>
+      </c>
+      <c r="H142" s="1" t="n">
+        <f aca="false">IF(F142*G142&lt;0,ABS(F142)+ABS(G142),G142-F142+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I142" s="1" t="n">
+        <f aca="false">E142/H142</f>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -11938,7 +11972,7 @@
         <v>1005|[卷139](9_筆記/资治通鉴139.html)|齊紀五|494|494|</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="n">
         <v>1006</v>
       </c>
@@ -11966,24 +12000,24 @@
       <c r="A142" s="1" t="n">
         <v>1007</v>
       </c>
-      <c r="B142" s="1" t="e">
+      <c r="B142" s="1" t="str">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷141</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D142" s="1" t="e">
+      <c r="D142" s="1" t="n">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E142" s="1" t="e">
+        <v>497</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I142" s="1" t="e">
+        <v>498</v>
+      </c>
+      <c r="I142" s="1" t="str">
         <f aca="false">A142&amp;"|"&amp;"["&amp;B142&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B142,"卷","")&amp;".html)|"&amp;C142&amp;"|"&amp;D142&amp;"|"&amp;E142&amp;"|"&amp;H142</f>
-        <v>#N/A</v>
+        <v>1007|[卷141](9_筆記/资治通鉴141.html)|齊紀七|497|498|</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="76972386"/>
-        <c:axId val="47824912"/>
+        <c:axId val="88833128"/>
+        <c:axId val="31850665"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="76972386"/>
+        <c:axId val="88833128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47824912"/>
+        <c:crossAx val="31850665"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="47824912"/>
+        <c:axId val="31850665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76972386"/>
+        <c:crossAx val="88833128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>643680</xdr:colOff>
+      <xdr:colOff>643320</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>202320</xdr:rowOff>
+      <xdr:rowOff>201960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4550400" cy="2735280"/>
+        <a:ext cx="4550040" cy="2734920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R142"/>
+  <dimension ref="A1:R143"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>798.156028368794</v>
+        <v>811.211267605634</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44817.1560283688</v>
+        <v>44830.2112676056</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1436.74354656248</v>
+        <v>1622.96299438093</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45455.7435465625</v>
+        <v>45641.9629943809</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>915.531914893617</v>
+        <v>930.507042253521</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44934.5319148936</v>
+        <v>44949.5070422535</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1575.11371156047</v>
+        <v>1779.2676166327</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45594.1137115605</v>
+        <v>45798.2676166327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1385.03546099291</v>
+        <v>1407.69014084507</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45404.0354609929</v>
+        <v>45426.6901408451</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>1897.97742988912</v>
+        <v>2143.97840188684</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>45916.9774298891</v>
+        <v>46162.9784018868</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2065.81560283688</v>
+        <v>2099.60563380282</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46084.8156028369</v>
+        <v>46118.6056338028</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2287.72006130013</v>
+        <v>2584.23642122934</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46306.7200613001</v>
+        <v>46603.2364212294</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3110.4609929078</v>
+        <v>3161.33802816901</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47129.4609929078</v>
+        <v>47180.338028169</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>3021.08193578948</v>
+        <v>3412.65091916375</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>47040.0819357895</v>
+        <v>47431.6509191638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3450.85106382979</v>
+        <v>3507.29577464789</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47469.8510638298</v>
+        <v>47526.2957746479</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>3141.00274545441</v>
+        <v>3548.11492511529</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>47160.0027454544</v>
+        <v>47567.1149251153</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3450.85106382979</v>
+        <v>3507.29577464789</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47469.8510638298</v>
+        <v>47526.2957746479</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>3141.00274545441</v>
+        <v>3548.11492511529</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>47160.0027454544</v>
+        <v>47567.1149251153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.7375886524823</v>
+        <v>11.9295774647887</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.30616941663319</v>
+        <v>2.60507703752958</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,6 +7953,40 @@
       <c r="I142" s="1" t="n">
         <f aca="false">E142/H142</f>
         <v>12</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B143" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B142)</f>
+        <v>卷142</v>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="E143" s="1" t="n">
+        <f aca="false">D143-C143+1</f>
+        <v>39</v>
+      </c>
+      <c r="F143" s="1" t="n">
+        <f aca="false">G142+1</f>
+        <v>499</v>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>499</v>
+      </c>
+      <c r="H143" s="1" t="n">
+        <f aca="false">IF(F143*G143&lt;0,ABS(F143)+ABS(G143),G143-F143+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I143" s="1" t="n">
+        <f aca="false">E143/H143</f>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -11996,7 +12030,7 @@
         <v>1006|[卷140](9_筆記/资治通鉴140.html)|齊紀六|495|496|</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="n">
         <v>1007</v>
       </c>
@@ -12024,24 +12058,24 @@
       <c r="A143" s="1" t="n">
         <v>1008</v>
       </c>
-      <c r="B143" s="1" t="e">
+      <c r="B143" s="1" t="str">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷142</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D143" s="1" t="e">
+      <c r="D143" s="1" t="n">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E143" s="1" t="e">
+        <v>499</v>
+      </c>
+      <c r="E143" s="1" t="n">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I143" s="1" t="e">
+        <v>499</v>
+      </c>
+      <c r="I143" s="1" t="str">
         <f aca="false">A143&amp;"|"&amp;"["&amp;B143&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B143,"卷","")&amp;".html)|"&amp;C143&amp;"|"&amp;D143&amp;"|"&amp;E143&amp;"|"&amp;H143</f>
-        <v>#N/A</v>
+        <v>1008|[卷142](9_筆記/资治通鉴142.html)|齊紀八|499|499|</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="88833128"/>
-        <c:axId val="31850665"/>
+        <c:axId val="10641576"/>
+        <c:axId val="13117452"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="88833128"/>
+        <c:axId val="10641576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31850665"/>
+        <c:crossAx val="13117452"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="31850665"/>
+        <c:axId val="13117452"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88833128"/>
+        <c:crossAx val="10641576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>643320</xdr:colOff>
+      <xdr:colOff>642960</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>201960</xdr:rowOff>
+      <xdr:rowOff>201600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4550040" cy="2734920"/>
+        <a:ext cx="4549680" cy="2734560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R143"/>
+  <dimension ref="A1:R144"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>811.211267605634</v>
+        <v>811.72027972028</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44830.2112676056</v>
+        <v>44830.7202797203</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1622.96299438093</v>
+        <v>1664.24609118769</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45641.9629943809</v>
+        <v>45683.2460911877</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>930.507042253521</v>
+        <v>931.090909090909</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44949.5070422535</v>
+        <v>44950.0909090909</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1779.2676166327</v>
+        <v>1824.52661361347</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45798.2676166327</v>
+        <v>45843.5266136135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1407.69014084507</v>
+        <v>1408.57342657343</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45426.6901408451</v>
+        <v>45427.5734265734</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>2143.97840188684</v>
+        <v>2198.51449927362</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>46162.9784018868</v>
+        <v>46217.5144992736</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2099.60563380282</v>
+        <v>2100.92307692308</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46118.6056338028</v>
+        <v>46119.9230769231</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2584.23642122934</v>
+        <v>2649.97130410624</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46603.2364212294</v>
+        <v>46668.9713041062</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3161.33802816901</v>
+        <v>3163.32167832168</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47180.338028169</v>
+        <v>47182.3216783217</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>3412.65091916375</v>
+        <v>3499.45807296288</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>47431.6509191638</v>
+        <v>47518.4580729629</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3507.29577464789</v>
+        <v>3509.4965034965</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47526.2957746479</v>
+        <v>47528.4965034965</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>3548.11492511529</v>
+        <v>3638.36785906522</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>47567.1149251153</v>
+        <v>47657.3678590652</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3507.29577464789</v>
+        <v>3509.4965034965</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47526.2957746479</v>
+        <v>47528.4965034965</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>3548.11492511529</v>
+        <v>3638.36785906522</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>47567.1149251153</v>
+        <v>47657.3678590652</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.9295774647887</v>
+        <v>11.9370629370629</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.60507703752958</v>
+        <v>2.67134204042968</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7987,6 +7987,40 @@
       <c r="I143" s="1" t="n">
         <f aca="false">E143/H143</f>
         <v>39</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B144" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B143)</f>
+        <v>卷143</v>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="E144" s="1" t="n">
+        <f aca="false">D144-C144+1</f>
+        <v>13</v>
+      </c>
+      <c r="F144" s="1" t="n">
+        <f aca="false">G143+1</f>
+        <v>500</v>
+      </c>
+      <c r="G144" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="H144" s="1" t="n">
+        <f aca="false">IF(F144*G144&lt;0,ABS(F144)+ABS(G144),G144-F144+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I144" s="1" t="n">
+        <f aca="false">E144/H144</f>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -12054,7 +12088,7 @@
         <v>1007|[卷141](9_筆記/资治通鉴141.html)|齊紀七|497|498|</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="n">
         <v>1008</v>
       </c>
@@ -12082,24 +12116,24 @@
       <c r="A144" s="1" t="n">
         <v>1009</v>
       </c>
-      <c r="B144" s="1" t="e">
+      <c r="B144" s="1" t="str">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷143</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D144" s="1" t="e">
+      <c r="D144" s="1" t="n">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E144" s="1" t="e">
+        <v>500</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I144" s="1" t="e">
+        <v>500</v>
+      </c>
+      <c r="I144" s="1" t="str">
         <f aca="false">A144&amp;"|"&amp;"["&amp;B144&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B144,"卷","")&amp;".html)|"&amp;C144&amp;"|"&amp;D144&amp;"|"&amp;E144&amp;"|"&amp;H144</f>
-        <v>#N/A</v>
+        <v>1009|[卷143](9_筆記/资治通鉴143.html)|齊紀九|500|500|</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
